--- a/report_forms/019_inventory_form--report_forms.xlsx
+++ b/report_forms/019_inventory_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -984,12 +984,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>item_status</t>
+          <t>item_status_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Item Status</t>
+          <t>Item Status 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>item_condition</t>
+          <t>item_condition_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Item Condition</t>
+          <t>Item Condition 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>item_subcategory</t>
+          <t>item_subcategory_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Item Subcategory</t>
+          <t>Item Subcategory 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>item_category</t>
+          <t>item_category_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Item Category</t>
+          <t>Item Category 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1105,7 +1105,7 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1283,7 +1283,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>item_status_choices</t>
+          <t>item_status_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1300,7 +1300,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>item_status_choices</t>
+          <t>item_status_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1317,7 +1317,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>item_status_choices</t>
+          <t>item_status_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1334,7 +1334,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>item_condition_choices</t>
+          <t>item_condition_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>item_condition_choices</t>
+          <t>item_condition_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1368,7 +1368,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>item_condition_choices</t>
+          <t>item_condition_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1385,7 +1385,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>item_category_choices</t>
+          <t>item_category_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1402,7 +1402,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>item_category_choices</t>
+          <t>item_category_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1419,7 +1419,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>item_category_choices</t>
+          <t>item_category_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
